--- a/data/trans_orig/IQ26A_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ26A_R2-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2519</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9619</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,76%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>5336</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2522</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10480</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2593</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9998</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,84%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5183</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2527</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9740</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16057</t>
+          <t>16641</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>104624</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>100188</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>107288</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,28%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,24%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>85996</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>80852</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>88810</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>81334</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>88739</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,16%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,24%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>104624</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>100067</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>107280</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185082</t>
+          <t>184498</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>194786</t>
+          <t>194932</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>109807</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>109807</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>109807</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91332</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91332</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91332</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>109807</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>109807</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>109807</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>31675</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24215</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>41482</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,54%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>23217</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>16489</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>30603</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>16634</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>31249</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,17%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,09%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>31675</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>22983</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>40123</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44856</t>
+          <t>45008</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66961</t>
+          <t>67185</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>222081</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>212274</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>229541</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,52%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,46%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>344</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>229988</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>222602</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>236716</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>221956</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>236571</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,83%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>222081</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>213633</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>230773</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>87,52%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>440000</t>
+          <t>439776</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>462105</t>
+          <t>461953</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14672</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9942</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21385</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,03%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>16946</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11166</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23686</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11191</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>23801</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>13,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>14672</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9398</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>21423</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,37%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24331</t>
+          <t>23848</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40623</t>
+          <t>40471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>126843</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>120130</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>131573</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,63%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>110602</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>103862</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>116382</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>103747</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>116357</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>86,71%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,43%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,25%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>126843</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>120092</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>132117</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,63%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>228440</t>
+          <t>228592</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>244732</t>
+          <t>245215</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34595</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26923</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>43306</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13,07%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>45220</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>36416</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>54939</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>36826</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>56241</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>23,39%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,83%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>28,41%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>34595</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>27175</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>43848</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,79%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67528</t>
+          <t>68110</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93502</t>
+          <t>93762</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>171454</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>162743</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>179126</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>78,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>86,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>148145</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>138426</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>156949</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>137124</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>156539</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>76,61%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>71,59%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>81,17%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>171454</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>162201</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>178874</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>83,21%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>305912</t>
+          <t>305652</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>331886</t>
+          <t>331304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>193365</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>193365</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>193365</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>86126</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>72698</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>102824</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>90719</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>75760</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>104758</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>78806</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>105613</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>13,63%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,38%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>86126</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>72335</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>101655</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>12,11%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>158159</t>
+          <t>155289</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>198043</t>
+          <t>197327</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>625001</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>608303</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>638429</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,89%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>85,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>859</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>574731</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>560692</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>589690</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>559837</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>586644</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>86,37%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>84,26%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,62%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>625001</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>609472</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>638792</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>87,89%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1178534</t>
+          <t>1179250</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1218418</t>
+          <t>1221288</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1069</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>711127</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>711127</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>711127</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>994</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>665450</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>665450</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>665450</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>711127</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>711127</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>711127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8321</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4592</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14328</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4666</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8954</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9228</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,75%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8321</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4633</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14628</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19649</t>
+          <t>19936</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>110254</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>104247</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>113983</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,92%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,13%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>119620</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>115332</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>122313</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>115058</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>122316</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,25%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,8%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>110254</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>103947</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>113942</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,98%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>223212</t>
+          <t>222925</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>234948</t>
+          <t>234549</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118575</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118575</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118575</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>124286</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>124286</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>124286</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118575</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118575</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118575</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25486</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18235</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>34324</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>15625</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10799</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22883</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10355</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>22786</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,61%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>25486</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>17927</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,55%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31233</t>
+          <t>31557</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52332</t>
+          <t>52330</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>241398</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>232560</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>248649</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,14%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,17%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>220625</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>213367</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>225451</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>213464</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>225895</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,39%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,31%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,43%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>241398</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>233254</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>248957</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,45%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>450802</t>
+          <t>450804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>471901</t>
+          <t>471577</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>266884</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>266884</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>266884</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>266884</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>266884</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>266884</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16591</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11055</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23917</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>21665</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14889</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29359</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>15302</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>29349</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>13,85%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>16591</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11124</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>23390</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30394</t>
+          <t>29241</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48690</t>
+          <t>49350</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141346</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>134020</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>146882</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,5%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>134769</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>127075</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>141545</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>127085</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>141132</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>86,15%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>90,48%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141346</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>134547</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>146813</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,5%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265681</t>
+          <t>265021</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>283977</t>
+          <t>285130</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>157937</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>157937</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>157937</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156434</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156434</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156434</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>157937</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>157937</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>157937</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29710</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22799</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>39266</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,67%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,82%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>30315</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22963</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>38597</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>22760</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>39247</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,53%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>29710</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>22254</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>38149</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,51%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48185</t>
+          <t>49531</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71871</t>
+          <t>71878</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>150245</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>140689</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>157156</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,49%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>78,18%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,33%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>141022</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>132740</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>148374</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>132090</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>148577</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>82,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>86,6%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>150245</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>141806</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>157701</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>83,49%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>279421</t>
+          <t>279414</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>303107</t>
+          <t>301761</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>85,9%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>80108</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>66216</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>94161</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11,07%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,15%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,02%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>72270</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>59395</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>86929</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>59649</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>86380</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,63%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>80108</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>67074</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>94857</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133547</t>
+          <t>133112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172507</t>
+          <t>171127</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>643244</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>629191</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>657136</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>88,93%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>86,98%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,85%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>887</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>616037</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>601378</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>628912</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>601927</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>628658</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>89,5%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,37%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,37%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>643244</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>628495</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>656278</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>88,93%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1239152</t>
+          <t>1240532</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1278112</t>
+          <t>1278547</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>723352</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>723352</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>723352</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>991</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>688307</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>688307</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>688307</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>723352</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>723352</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>723352</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2537</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9421</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4502</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9168</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10151</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,75%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5309</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2632</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9808</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15546</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>111342</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>107230</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>114114</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,45%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,92%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>115614</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>110948</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>118611</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>109965</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>118298</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,25%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,37%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>111342</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>106843</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>114019</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,45%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>221222</t>
+          <t>221633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>231358</t>
+          <t>231527</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>116651</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>116651</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>116651</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>120116</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>120116</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>120116</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>116651</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>116651</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>116651</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>37548</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29676</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>47130</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,26%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>30282</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>23346</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>40082</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>23183</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>39665</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>14,38%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,09%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,04%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>37548</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>28454</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>48382</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,55%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56389</t>
+          <t>56067</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81068</t>
+          <t>81086</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>220513</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>210931</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>228385</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,74%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,5%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>180235</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>170435</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>187171</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>170852</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>187334</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>85,62%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>80,96%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,91%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>220513</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>209679</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>229607</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,45%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>387510</t>
+          <t>387492</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>412189</t>
+          <t>412511</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,03%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29749</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22476</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>38920</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,72%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>29360</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>21821</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38181</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>22005</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>37684</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>15,59%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>29749</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>22944</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>39265</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>15,83%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48823</t>
+          <t>47279</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70818</t>
+          <t>71045</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158123</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>148952</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165396</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>84,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,28%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,04%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>158922</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>166461</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>150598</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>166277</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>84,41%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>79,72%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>88,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>158123</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>148607</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>164928</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>84,17%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>305336</t>
+          <t>305109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>327331</t>
+          <t>328875</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,43%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187872</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187872</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187872</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188282</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188282</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188282</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187872</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187872</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187872</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34392</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26445</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>45456</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,76%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>28066</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>46714</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>28363</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>46737</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>21,22%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>27,04%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>34392</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>26399</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>45060</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59609</t>
+          <t>58745</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83199</t>
+          <t>82999</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>139656</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>128592</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>147603</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,24%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>73,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>136088</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>126037</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>144685</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>126014</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>144388</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>78,78%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>72,96%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,75%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>139656</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>128988</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>147649</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>80,24%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>263600</t>
+          <t>263800</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>287190</t>
+          <t>288054</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172751</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172751</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172751</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>106996</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>90733</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>122750</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12,32%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>100807</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>87132</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>116586</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>87884</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>117410</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>14,57%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,6%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>106996</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>91825</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>125082</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>186417</t>
+          <t>186116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>229676</t>
+          <t>232128</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>629636</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>613882</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>645899</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>85,47%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>83,34%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>87,68%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>892</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>590860</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>575081</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>604535</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>574257</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>603783</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>85,43%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>83,14%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>87,4%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>902</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>629636</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>611550</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>644807</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>85,47%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1198623</t>
+          <t>1196171</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1241882</t>
+          <t>1242183</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,97%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>736632</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>736632</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>736632</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1040</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>691667</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>691667</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>691667</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1053</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>736632</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>736632</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>736632</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2604</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4502</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,74%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>535</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10274</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8171</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10775</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12191</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9250</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13421</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>88,65%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>67,26%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,59%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12754</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10556</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13194</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>24945</t>
+          <t>21429</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21593</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26494</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10775</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10775</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10775</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13752</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13752</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13752</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13194</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13194</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13194</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>26946</t>
+          <t>23503</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26946</t>
+          <t>23503</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26946</t>
+          <t>23503</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8463</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5007</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13865</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,68%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>35,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10751</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6807</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16567</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>31,31%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>19,82%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>48,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8873</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>12387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>19625</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>11879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27974</t>
+          <t>23087</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>31016</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25614</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>34472</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>78,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>64,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,32%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>23589</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17773</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>27533</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>68,69%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>51,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>35890</t>
+          <t>22242</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30928</t>
+          <t>18211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39608</t>
+          <t>25474</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>59479</t>
+          <t>53258</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51130</t>
+          <t>46990</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65232</t>
+          <t>58198</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39479</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39479</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39479</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>34340</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>34340</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>34340</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11983</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6903</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18293</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>22,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>34,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7686</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3880</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12360</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,21%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,89%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13015</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19847</t>
+          <t>12595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20701</t>
+          <t>19822</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13410</t>
+          <t>13730</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29451</t>
+          <t>27624</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>41310</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>35000</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>46390</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>77,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>65,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>32321</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>27647</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>36127</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>80,79%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>69,11%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>90,3%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42902</t>
+          <t>30616</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36070</t>
+          <t>25860</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48879</t>
+          <t>34108</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>75223</t>
+          <t>71927</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66473</t>
+          <t>64125</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>82514</t>
+          <t>78019</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,03%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>53293</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>53293</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>53293</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>40007</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>40007</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>40007</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12338</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7489</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19249</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,06%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>14310</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9417</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20140</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>26,73%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>37,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18257</t>
+          <t>21056</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,22 +7668,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>26069</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19458</t>
+          <t>19515</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34234</t>
+          <t>35594</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>62088</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>55177</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>66937</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,94%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>39237</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>33407</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>44130</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>73,27%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>65020</t>
+          <t>41515</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58522</t>
+          <t>35204</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69681</t>
+          <t>46305</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,27 +7781,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>104257</t>
+          <t>103604</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96092</t>
+          <t>95093</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>110868</t>
+          <t>111172</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>74426</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>74426</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>74426</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>53547</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>53547</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>53547</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>56260</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>56260</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>56260</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>130326</t>
+          <t>130687</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>130326</t>
+          <t>130687</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>130326</t>
+          <t>130687</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33286</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24706</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>42485</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>13,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>23,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>34308</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>26286</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>44143</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>24,22%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>31,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>34087</t>
+          <t>32512</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25523</t>
+          <t>25021</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45615</t>
+          <t>42385</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>68395</t>
+          <t>65798</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56479</t>
+          <t>53818</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83764</t>
+          <t>79361</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>144687</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>135488</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>153267</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,3%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>76,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>86,12%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>107338</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>97503</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>115360</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>75,78%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>68,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>156566</t>
+          <t>105530</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145038</t>
+          <t>95657</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>165130</t>
+          <t>113021</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>263904</t>
+          <t>250217</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248535</t>
+          <t>236654</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>275820</t>
+          <t>262197</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>177973</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>177973</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>177973</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>141646</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>141646</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>141646</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>190653</t>
+          <t>138042</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>190653</t>
+          <t>138042</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>190653</t>
+          <t>138042</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>332299</t>
+          <t>316015</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>332299</t>
+          <t>316015</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>332299</t>
+          <t>316015</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
